--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:16:18+00:00</t>
+    <t>2025-08-22T11:39:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,6 +262,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">PersonFamilyRequired:L'élément name.family pour un professionnel doit être présent au moins une fois pour identifier la personne. {name.item.family.count() = 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -409,126 +413,11 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PN {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name}
 </t>
   </si>
   <si>
     <t>Identité de la personne physique responsable</t>
-  </si>
-  <si>
-    <t>Person.name.nullFlavor</t>
-  </si>
-  <si>
-    <t>Person.name.use</t>
-  </si>
-  <si>
-    <t>Use Code</t>
-  </si>
-  <si>
-    <t>A set of codes advising a system or user which name in a set of like names to select for a given purpose. A name without specific use code might be a default name useful for any purpose, but a name with a specific use code would be preferred for that respective purpose</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAEntityNameUse</t>
-  </si>
-  <si>
-    <t>EN.use</t>
-  </si>
-  <si>
-    <t>Person.name.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
-  </si>
-  <si>
-    <t>A series of items that constitute the name.</t>
-  </si>
-  <si>
-    <t>EN.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EN-1:Can only have only one of the possible item elements in each choice {(delimiter | family | given | prefix | suffix | xmlText).count() = 1}
-</t>
-  </si>
-  <si>
-    <t>Person.name.item.delimiter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
-</t>
-  </si>
-  <si>
-    <t>EN.item.delimiter</t>
-  </si>
-  <si>
-    <t>Person.name.item.family</t>
-  </si>
-  <si>
-    <t>Nom de famille ou nom d’usage</t>
-  </si>
-  <si>
-    <t>EN.item.family</t>
-  </si>
-  <si>
-    <t>Person.name.item.given</t>
-  </si>
-  <si>
-    <t>Prénom</t>
-  </si>
-  <si>
-    <t>EN.item.given</t>
-  </si>
-  <si>
-    <t>Person.name.item.prefix</t>
-  </si>
-  <si>
-    <t>Civilité</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
-  </si>
-  <si>
-    <t>EN.item.prefix</t>
-  </si>
-  <si>
-    <t>Person.name.item.suffix</t>
-  </si>
-  <si>
-    <t>Titre</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J246-Titre-CISIS/FHIR/JDV-J246-Titre-CISIS</t>
-  </si>
-  <si>
-    <t>EN.item.suffix</t>
-  </si>
-  <si>
-    <t>Person.name.item.xmlText</t>
-  </si>
-  <si>
-    <t>Allows for mixed text content</t>
-  </si>
-  <si>
-    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
-  </si>
-  <si>
-    <t>EN.item.xmlText</t>
-  </si>
-  <si>
-    <t>Person.name.validTime</t>
-  </si>
-  <si>
-    <t>Valid Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
-</t>
-  </si>
-  <si>
-    <t>An interval of time specifying the time during which the name is or was used for the entity. This accomodates the fact that people change names for people, places and things.</t>
-  </si>
-  <si>
-    <t>EN.validTime</t>
   </si>
   <si>
     <t>Person.sdtcDesc</t>
@@ -893,7 +782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.53125" customWidth="true" bestFit="true"/>
@@ -921,7 +810,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1144,25 +1033,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1180,11 +1069,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1211,11 +1100,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1233,7 +1122,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1253,10 +1142,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1279,11 +1168,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1334,7 +1223,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1354,10 +1243,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1380,11 +1269,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1435,7 +1324,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1455,17 +1344,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>80</v>
@@ -1483,11 +1372,11 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1514,11 +1403,11 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1536,7 +1425,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1556,17 +1445,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1584,11 +1473,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1639,7 +1528,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1659,17 +1548,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1687,11 +1576,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1742,7 +1631,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1762,17 +1651,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1790,11 +1679,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1803,7 +1692,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1845,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1865,17 +1754,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1893,11 +1782,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1948,7 +1837,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1968,10 +1857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1994,11 +1883,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2049,7 +1938,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2069,10 +1958,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2083,7 +1972,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2095,7 +1984,7 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -2106,7 +1995,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2124,11 +2013,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2146,7 +2035,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2166,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2192,7 +2081,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2203,7 +2092,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2221,11 +2110,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2243,7 +2132,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2263,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2289,10 +2178,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2344,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2364,18 +2253,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2392,11 +2279,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2423,11 +2310,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2445,7 +2334,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2465,18 +2354,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" t="s" s="2">
-        <v>133</v>
-      </c>
+      <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
@@ -2493,11 +2380,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2524,29 +2411,31 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2566,21 +2455,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2592,11 +2483,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2623,13 +2514,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2647,19 +2536,19 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>74</v>
@@ -2667,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2681,7 +2570,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2693,10 +2582,12 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2746,7 +2637,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2766,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2777,7 +2668,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>75</v>
@@ -2792,12 +2683,12 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M19" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2847,13 +2738,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2867,21 +2758,23 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2893,12 +2786,12 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M20" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2924,13 +2817,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2948,13 +2839,13 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
@@ -2968,21 +2859,23 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2994,12 +2887,12 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3025,11 +2918,13 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>74</v>
@@ -3047,13 +2942,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3067,21 +2962,23 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3093,12 +2990,12 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3124,11 +3021,13 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
@@ -3146,13 +3045,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3166,21 +3065,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3192,22 +3093,20 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3249,7 +3148,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3269,23 +3168,23 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3297,11 +3196,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3352,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3372,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3386,7 +3285,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3398,11 +3297,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3453,13 +3352,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3473,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3484,10 +3383,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3499,12 +3398,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="M26" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3512,7 +3409,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3554,13 +3451,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3574,18 +3471,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E27" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
@@ -3602,12 +3497,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3615,7 +3508,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3633,11 +3526,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3655,7 +3550,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3675,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3686,10 +3581,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3701,12 +3596,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3756,13 +3649,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3771,1018 +3664,6 @@
         <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L29" s="2"/>
-      <c r="M29" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y30" s="2"/>
-      <c r="Z30" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L31" s="2"/>
-      <c r="M31" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK38" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:39:32+00:00</t>
+    <t>2025-08-22T13:00:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T13:00:58+00:00</t>
+    <t>2025-08-22T15:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,10 +262,6 @@
     <t>*</t>
   </si>
   <si>
-    <t xml:space="preserve">PersonFamilyRequired:L'élément name.family pour un professionnel doit être présent au moins une fois pour identifier la personne. {name.item.family.count() = 1}
-</t>
-  </si>
-  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -413,11 +409,126 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PN {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name}
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name
 </t>
   </si>
   <si>
     <t>Identité de la personne physique responsable</t>
+  </si>
+  <si>
+    <t>Person.name.nullFlavor</t>
+  </si>
+  <si>
+    <t>Person.name.use</t>
+  </si>
+  <si>
+    <t>Use Code</t>
+  </si>
+  <si>
+    <t>A set of codes advising a system or user which name in a set of like names to select for a given purpose. A name without specific use code might be a default name useful for any purpose, but a name with a specific use code would be preferred for that respective purpose</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAEntityNameUse</t>
+  </si>
+  <si>
+    <t>EN.use</t>
+  </si>
+  <si>
+    <t>Person.name.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>A series of items that constitute the name.</t>
+  </si>
+  <si>
+    <t>EN.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN-1:Can only have only one of the possible item elements in each choice {(delimiter | family | given | prefix | suffix | xmlText).count() = 1}
+</t>
+  </si>
+  <si>
+    <t>Person.name.item.delimiter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
+</t>
+  </si>
+  <si>
+    <t>EN.item.delimiter</t>
+  </si>
+  <si>
+    <t>Person.name.item.family</t>
+  </si>
+  <si>
+    <t>Nom de famille ou nom d’usage</t>
+  </si>
+  <si>
+    <t>EN.item.family</t>
+  </si>
+  <si>
+    <t>Person.name.item.given</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>EN.item.given</t>
+  </si>
+  <si>
+    <t>Person.name.item.prefix</t>
+  </si>
+  <si>
+    <t>Civilité</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
+  </si>
+  <si>
+    <t>EN.item.prefix</t>
+  </si>
+  <si>
+    <t>Person.name.item.suffix</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J246-Titre-CISIS/FHIR/JDV-J246-Titre-CISIS</t>
+  </si>
+  <si>
+    <t>EN.item.suffix</t>
+  </si>
+  <si>
+    <t>Person.name.item.xmlText</t>
+  </si>
+  <si>
+    <t>Allows for mixed text content</t>
+  </si>
+  <si>
+    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
+  </si>
+  <si>
+    <t>EN.item.xmlText</t>
+  </si>
+  <si>
+    <t>Person.name.validTime</t>
+  </si>
+  <si>
+    <t>Valid Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>An interval of time specifying the time during which the name is or was used for the entity. This accomodates the fact that people change names for people, places and things.</t>
+  </si>
+  <si>
+    <t>EN.validTime</t>
   </si>
   <si>
     <t>Person.sdtcDesc</t>
@@ -782,7 +893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK28"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.53125" customWidth="true" bestFit="true"/>
@@ -810,7 +921,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1033,47 +1144,47 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1100,29 +1211,29 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF3" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE3" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF3" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1142,10 +1253,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1168,11 +1279,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1223,7 +1334,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1243,10 +1354,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1269,11 +1380,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1435,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1344,39 +1455,39 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1403,29 +1514,29 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1445,39 +1556,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1528,7 +1639,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1548,39 +1659,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1631,7 +1742,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1651,39 +1762,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1692,49 +1803,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1754,17 +1865,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1782,11 +1893,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1837,7 +1948,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1857,10 +1968,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1883,11 +1994,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1938,7 +2049,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1958,10 +2069,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1972,7 +2083,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1984,7 +2095,7 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1995,7 +2106,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2013,11 +2124,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2035,7 +2146,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2055,10 +2166,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2081,7 +2192,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2092,7 +2203,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2110,11 +2221,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2132,7 +2243,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2152,10 +2263,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2178,10 +2289,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2233,7 +2344,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2253,16 +2364,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2279,11 +2392,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2310,13 +2423,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2334,7 +2445,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2354,16 +2465,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
@@ -2380,11 +2493,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2411,13 +2524,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2435,7 +2546,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2455,23 +2566,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2483,11 +2592,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2514,11 +2623,13 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2536,19 +2647,19 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>74</v>
@@ -2556,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2570,7 +2681,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2582,12 +2693,10 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2637,7 +2746,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2657,10 +2766,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2668,7 +2777,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>75</v>
@@ -2683,12 +2792,12 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2738,13 +2847,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2758,23 +2867,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E20" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2786,12 +2893,12 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" t="s" s="2">
-        <v>87</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2817,11 +2924,13 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2839,13 +2948,13 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
@@ -2859,23 +2968,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E21" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2887,12 +2994,12 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" t="s" s="2">
-        <v>103</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -2918,13 +3025,11 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>74</v>
@@ -2942,13 +3047,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -2962,23 +3067,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E22" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -2990,12 +3093,12 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L22" s="2"/>
-      <c r="M22" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3021,13 +3124,11 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
@@ -3045,13 +3146,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3065,23 +3166,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E23" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3093,20 +3192,22 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="M23" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3148,7 +3249,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3168,23 +3269,23 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3196,11 +3297,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3251,7 +3352,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3271,10 +3372,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3285,7 +3386,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3297,11 +3398,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3352,13 +3453,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3372,10 +3473,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3383,10 +3484,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3398,10 +3499,12 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3409,7 +3512,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3451,13 +3554,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3471,16 +3574,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
@@ -3497,10 +3602,12 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3508,7 +3615,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3526,13 +3633,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3550,7 +3655,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3570,10 +3675,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3581,10 +3686,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3596,10 +3701,12 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3649,13 +3756,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3664,6 +3771,1018 @@
         <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
+      <c r="Z30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T15:38:31+00:00</t>
+    <t>2025-08-22T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -262,6 +262,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">PersonFamilyRequired:L'élément name.family pour un professionnel doit être présent au moins une fois pour identifier la personne. {name.item.family.count() = 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -409,126 +413,11 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/PN {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-name}
 </t>
   </si>
   <si>
     <t>Identité de la personne physique responsable</t>
-  </si>
-  <si>
-    <t>Person.name.nullFlavor</t>
-  </si>
-  <si>
-    <t>Person.name.use</t>
-  </si>
-  <si>
-    <t>Use Code</t>
-  </si>
-  <si>
-    <t>A set of codes advising a system or user which name in a set of like names to select for a given purpose. A name without specific use code might be a default name useful for any purpose, but a name with a specific use code would be preferred for that respective purpose</t>
-  </si>
-  <si>
-    <t>http://hl7.org/cda/stds/core/ValueSet/CDAEntityNameUse</t>
-  </si>
-  <si>
-    <t>EN.use</t>
-  </si>
-  <si>
-    <t>Person.name.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
-  </si>
-  <si>
-    <t>A series of items that constitute the name.</t>
-  </si>
-  <si>
-    <t>EN.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EN-1:Can only have only one of the possible item elements in each choice {(delimiter | family | given | prefix | suffix | xmlText).count() = 1}
-</t>
-  </si>
-  <si>
-    <t>Person.name.item.delimiter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
-</t>
-  </si>
-  <si>
-    <t>EN.item.delimiter</t>
-  </si>
-  <si>
-    <t>Person.name.item.family</t>
-  </si>
-  <si>
-    <t>Nom de famille ou nom d’usage</t>
-  </si>
-  <si>
-    <t>EN.item.family</t>
-  </si>
-  <si>
-    <t>Person.name.item.given</t>
-  </si>
-  <si>
-    <t>Prénom</t>
-  </si>
-  <si>
-    <t>EN.item.given</t>
-  </si>
-  <si>
-    <t>Person.name.item.prefix</t>
-  </si>
-  <si>
-    <t>Civilité</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
-  </si>
-  <si>
-    <t>EN.item.prefix</t>
-  </si>
-  <si>
-    <t>Person.name.item.suffix</t>
-  </si>
-  <si>
-    <t>Titre</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J246-Titre-CISIS/FHIR/JDV-J246-Titre-CISIS</t>
-  </si>
-  <si>
-    <t>EN.item.suffix</t>
-  </si>
-  <si>
-    <t>Person.name.item.xmlText</t>
-  </si>
-  <si>
-    <t>Allows for mixed text content</t>
-  </si>
-  <si>
-    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
-  </si>
-  <si>
-    <t>EN.item.xmlText</t>
-  </si>
-  <si>
-    <t>Person.name.validTime</t>
-  </si>
-  <si>
-    <t>Valid Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
-</t>
-  </si>
-  <si>
-    <t>An interval of time specifying the time during which the name is or was used for the entity. This accomodates the fact that people change names for people, places and things.</t>
-  </si>
-  <si>
-    <t>EN.validTime</t>
   </si>
   <si>
     <t>Person.sdtcDesc</t>
@@ -893,7 +782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.53125" customWidth="true" bestFit="true"/>
@@ -921,7 +810,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -1144,25 +1033,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1180,11 +1069,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1211,11 +1100,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1233,7 +1122,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1253,10 +1142,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1279,11 +1168,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1334,7 +1223,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1354,10 +1243,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1380,11 +1269,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1435,7 +1324,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1455,17 +1344,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>80</v>
@@ -1483,11 +1372,11 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1514,11 +1403,11 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1536,7 +1425,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1556,17 +1445,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1584,11 +1473,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1639,7 +1528,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1659,17 +1548,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1687,11 +1576,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1742,7 +1631,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1762,17 +1651,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1790,11 +1679,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1803,7 +1692,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1845,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1865,17 +1754,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1893,11 +1782,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1948,7 +1837,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1968,10 +1857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1994,11 +1883,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2049,7 +1938,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2069,10 +1958,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2083,7 +1972,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2095,7 +1984,7 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -2106,7 +1995,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2124,11 +2013,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2146,7 +2035,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2166,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2192,7 +2081,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2203,7 +2092,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2221,11 +2110,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2243,7 +2132,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2263,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2289,10 +2178,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2344,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2364,18 +2253,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2392,11 +2279,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2423,11 +2310,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2445,7 +2334,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2465,18 +2354,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" t="s" s="2">
-        <v>133</v>
-      </c>
+      <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
@@ -2493,11 +2380,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2524,29 +2411,31 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2566,21 +2455,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2592,11 +2483,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2623,13 +2514,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2647,19 +2536,19 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>141</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>74</v>
@@ -2667,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2681,7 +2570,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2693,10 +2582,12 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2746,7 +2637,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2766,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2777,7 +2668,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>75</v>
@@ -2792,12 +2683,12 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M19" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2847,13 +2738,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2867,21 +2758,23 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2893,12 +2786,12 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M20" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2924,13 +2817,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2948,13 +2839,13 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
@@ -2968,21 +2859,23 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2994,12 +2887,12 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M21" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L21" s="2"/>
+      <c r="M21" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3025,11 +2918,13 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>74</v>
@@ -3047,13 +2942,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3067,21 +2962,23 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3093,12 +2990,12 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="M22" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3124,11 +3021,13 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
@@ -3146,13 +3045,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3166,21 +3065,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3192,22 +3093,20 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3249,7 +3148,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3269,23 +3168,23 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3297,11 +3196,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>166</v>
+        <v>118</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3352,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3372,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3386,7 +3285,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3398,11 +3297,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3453,13 +3352,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3473,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3484,10 +3383,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3499,12 +3398,10 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="M26" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3512,7 +3409,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -3554,13 +3451,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3574,18 +3471,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E27" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
@@ -3602,12 +3497,10 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3615,7 +3508,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3633,11 +3526,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3655,7 +3550,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3675,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3686,10 +3581,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3701,12 +3596,10 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3756,13 +3649,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3771,1018 +3664,6 @@
         <v>74</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="F29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L29" s="2"/>
-      <c r="M29" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q30" s="2"/>
-      <c r="R30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y30" s="2"/>
-      <c r="Z30" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L31" s="2"/>
-      <c r="M31" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
-      <c r="P36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
-      <c r="P37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C38" s="2"/>
-      <c r="D38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK38" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T16:16:41+00:00</t>
+    <t>2025-08-25T07:57:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T07:57:03+00:00</t>
+    <t>2025-08-25T14:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
